--- a/exit_interview_templates/035_energy_efficiency_specialist_exit_offboarding_form--exit_interview_templates.xlsx
+++ b/exit_interview_templates/035_energy_efficiency_specialist_exit_offboarding_form--exit_interview_templates.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -1102,7 +1102,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:C23"/>
+  <dimension ref="A1:C22"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="33" customWidth="1" min="1" max="1"/>
@@ -1198,17 +1198,17 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>current_job_title_choices</t>
+          <t>reason_for_departure_choices</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>energy_management_specialist</t>
+          <t>relocation</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>Energy Management Specialist</t>
+          <t>Relocation</t>
         </is>
       </c>
     </row>
@@ -1220,12 +1220,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>relocation</t>
+          <t>career_change</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>Relocation</t>
+          <t>Career Change</t>
         </is>
       </c>
     </row>
@@ -1237,12 +1237,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>career_change</t>
+          <t>job_elimination</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>Career Change</t>
+          <t>Job Elimination</t>
         </is>
       </c>
     </row>
@@ -1254,12 +1254,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>job_elimination</t>
+          <t>retirement</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>Job Elimination</t>
+          <t>Retirement</t>
         </is>
       </c>
     </row>
@@ -1271,29 +1271,29 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>retirement</t>
+          <t>resignation</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>Retirement</t>
+          <t>Resignation</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>reason_for_departure_choices</t>
+          <t>job_performance_rating_choices</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>resignation</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>Resignation</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1305,12 +1305,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1322,12 +1322,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1339,12 +1339,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1356,29 +1356,29 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>job_performance_rating_choices</t>
+          <t>job_satisfaction_rating_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -1390,12 +1390,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -1407,12 +1407,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -1424,12 +1424,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -1441,29 +1441,29 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>5</t>
         </is>
       </c>
     </row>
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>job_satisfaction_rating_choices</t>
+          <t>recommendation_choices</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>true</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1475,27 +1475,10 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>true</t>
+          <t>false</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
-        <is>
-          <t>True</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>recommendation_choices</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>false</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
         <is>
           <t>False</t>
         </is>
